--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\template_state_3.3\elec\RQSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{562808FB-A288-4193-89CB-88C9B71EB5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B96A7BF-FD31-43E9-A2B8-B572DDA1D947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="360" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,127 +36,127 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="41">
   <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>Each U.S. state that has an RPS defines the sources that qualify for that RPS, leading to</t>
+  </si>
+  <si>
+    <t>Electricity Source</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>solar PV</t>
+  </si>
+  <si>
+    <t>solar thermal</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>petroleum</t>
+  </si>
+  <si>
+    <t>natural gas peaker</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>The non-BAU version of this variable supports a boolean policy lever and is intended to be set by the</t>
+  </si>
+  <si>
     <t>RQSD BAU RPS Qualifying Source Definitions</t>
   </si>
   <si>
+    <t>RQSD RPS Qualifying Source Definitions</t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>onshore wind</t>
+  </si>
+  <si>
+    <t>offshore wind</t>
+  </si>
+  <si>
+    <t>differences between states.  Here, we use a "clean energy standard"</t>
+  </si>
+  <si>
+    <t>(counting everything except fossil fuels) as our definition for the BAU case.</t>
+  </si>
+  <si>
+    <t>model user.  The example we include uses only wind, solar, and geothermal.</t>
+  </si>
+  <si>
+    <t>Hydro is excluded because of limited potential for new large hydro and land use impacts.</t>
+  </si>
+  <si>
+    <t>Biomass is excluded because it is not truly carbon-neutral, and it has other issues, such as</t>
+  </si>
+  <si>
+    <t>local air quality impacts and land use challenges.</t>
+  </si>
+  <si>
+    <t>Nuclear is excluded because of the need to manage nuclear waste.</t>
+  </si>
+  <si>
+    <t>see notes</t>
+  </si>
+  <si>
+    <t>crude oil</t>
+  </si>
+  <si>
+    <t>heavy or residual fuel oil</t>
+  </si>
+  <si>
+    <t>municipal solid waste</t>
+  </si>
+  <si>
+    <t>Qualifies for RPS (Boolean)</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>hard coal w CCS</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle w CCS</t>
+  </si>
+  <si>
+    <t>biomass w CCS</t>
+  </si>
+  <si>
+    <t>lignite w CCS</t>
+  </si>
+  <si>
+    <t>small modular reactor</t>
+  </si>
+  <si>
+    <t>hydrogen combustion turbine</t>
+  </si>
+  <si>
+    <t>hydrogen combined cycle</t>
+  </si>
+  <si>
     <t>Louisiana</t>
-  </si>
-  <si>
-    <t>RQSD RPS Qualifying Source Definitions</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>see notes</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Each U.S. state that has an RPS defines the sources that qualify for that RPS, leading to</t>
-  </si>
-  <si>
-    <t>differences between states.  Here, we use a "clean energy standard"</t>
-  </si>
-  <si>
-    <t>(counting everything except fossil fuels) as our definition for the BAU case.</t>
-  </si>
-  <si>
-    <t>The non-BAU version of this variable supports a boolean policy lever and is intended to be set by the</t>
-  </si>
-  <si>
-    <t>model user.  The example we include uses only wind, solar, and geothermal.</t>
-  </si>
-  <si>
-    <t>Hydro is excluded because of limited potential for new large hydro and land use impacts.</t>
-  </si>
-  <si>
-    <t>Biomass is excluded because it is not truly carbon-neutral, and it has other issues, such as</t>
-  </si>
-  <si>
-    <t>local air quality impacts and land use challenges.</t>
-  </si>
-  <si>
-    <t>Nuclear is excluded because of the need to manage nuclear waste.</t>
-  </si>
-  <si>
-    <t>Electricity Source</t>
-  </si>
-  <si>
-    <t>Qualifies for RPS (Boolean)</t>
-  </si>
-  <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>natural gas steam turbine</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle</t>
-  </si>
-  <si>
-    <t>nuclear</t>
-  </si>
-  <si>
-    <t>hydro</t>
-  </si>
-  <si>
-    <t>onshore wind</t>
-  </si>
-  <si>
-    <t>solar PV</t>
-  </si>
-  <si>
-    <t>solar thermal</t>
-  </si>
-  <si>
-    <t>biomass</t>
-  </si>
-  <si>
-    <t>geothermal</t>
-  </si>
-  <si>
-    <t>petroleum</t>
-  </si>
-  <si>
-    <t>natural gas peaker</t>
-  </si>
-  <si>
-    <t>lignite</t>
-  </si>
-  <si>
-    <t>offshore wind</t>
-  </si>
-  <si>
-    <t>crude oil</t>
-  </si>
-  <si>
-    <t>heavy or residual fuel oil</t>
-  </si>
-  <si>
-    <t>municipal solid waste</t>
-  </si>
-  <si>
-    <t>hard coal w CCS</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle w CCS</t>
-  </si>
-  <si>
-    <t>biomass w CCS</t>
-  </si>
-  <si>
-    <t>lignite w CCS</t>
-  </si>
-  <si>
-    <t>small modular reactor</t>
-  </si>
-  <si>
-    <t>hydrogen combustion turbine</t>
-  </si>
-  <si>
-    <t>hydrogen combined cycle</t>
   </si>
 </sst>
 </file>
@@ -215,7 +214,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -534,91 +533,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="84.5703125" customWidth="1"/>
+    <col min="2" max="2" width="84.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C1" s="5">
-        <v>45194</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45237</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
       <c r="B5" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -628,208 +627,208 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" customWidth="1"/>
-    <col min="2" max="2" width="28.42578125" customWidth="1"/>
+    <col min="1" max="1" width="25.40625" customWidth="1"/>
+    <col min="2" max="2" width="28.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
         <v>15</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>29</v>
       </c>
       <c r="B14">
         <f>B2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
         <v>33</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A20" t="s">
         <v>34</v>
       </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A21" t="s">
         <v>35</v>
       </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A22" t="s">
         <v>36</v>
       </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A23" t="s">
         <v>37</v>
       </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="B24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A25" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -846,208 +845,208 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" customWidth="1"/>
-    <col min="2" max="2" width="28.42578125" customWidth="1"/>
+    <col min="1" max="1" width="25.40625" customWidth="1"/>
+    <col min="2" max="2" width="28.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
         <v>15</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>29</v>
       </c>
       <c r="B14">
         <f>B2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
         <v>33</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A20" t="s">
         <v>34</v>
       </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A21" t="s">
         <v>35</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A22" t="s">
         <v>36</v>
       </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A23" t="s">
         <v>37</v>
       </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="B24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A25" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="B25">
         <v>1</v>

--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\elec\RQSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AZ\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B96A7BF-FD31-43E9-A2B8-B572DDA1D947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1C1883F-7E71-4FCA-A921-F770E15A1675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="360" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -156,7 +156,7 @@
     <t>hydrogen combined cycle</t>
   </si>
   <si>
-    <t>Louisiana</t>
+    <t>Arizona</t>
   </si>
 </sst>
 </file>

--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AZ\elec\RQSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1C1883F-7E71-4FCA-A921-F770E15A1675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F6E1902-2A2F-435F-A6A4-97B66FBBB95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="360" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12195" yWindow="225" windowWidth="16605" windowHeight="17055" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -156,7 +156,7 @@
     <t>hydrogen combined cycle</t>
   </si>
   <si>
-    <t>Arizona</t>
+    <t>Louisiana</t>
   </si>
 </sst>
 </file>
@@ -533,12 +533,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="84.54296875" customWidth="1"/>
+    <col min="2" max="2" width="84.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -546,15 +546,15 @@
         <v>40</v>
       </c>
       <c r="C1" s="5">
-        <v>45237</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+        <v>45302</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,55 +562,55 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -627,13 +627,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.40625" customWidth="1"/>
-    <col min="2" max="2" width="28.40625" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -641,7 +641,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -649,7 +649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -657,7 +657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -665,23 +665,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -689,7 +689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -697,7 +697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -705,7 +705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -713,7 +713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -721,7 +721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -737,7 +737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -754,7 +754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -786,7 +786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -794,7 +794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -802,7 +802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -818,7 +818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
@@ -826,7 +826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>39</v>
       </c>
@@ -845,13 +845,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.40625" customWidth="1"/>
-    <col min="2" max="2" width="28.40625" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -859,7 +859,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -867,7 +867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -891,7 +891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -907,7 +907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -915,7 +915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -923,7 +923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -939,7 +939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -947,7 +947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -972,7 +972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>39</v>
       </c>

--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D3063A9-6546-40AA-B6F8-C5126BBFB92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3260D85-398C-490C-9D06-F836C394DEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2265" windowWidth="19965" windowHeight="7170" firstSheet="4" activeTab="6" xr2:uid="{926FECFB-B71C-4A2C-ACA6-D14493392182}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="2" activeTab="5" xr2:uid="{926FECFB-B71C-4A2C-ACA6-D14493392182}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1008,7 +1008,7 @@
         <v>73</v>
       </c>
       <c r="C1" s="12">
-        <v>45533</v>
+        <v>45721</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>39</v>
@@ -5577,7 +5577,7 @@
         <v>0</v>
       </c>
       <c r="AT25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU25">
         <v>0</v>
@@ -5732,7 +5732,7 @@
         <v>0</v>
       </c>
       <c r="AT26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU26">
         <v>0</v>
@@ -9725,7 +9725,7 @@
         <v>0</v>
       </c>
       <c r="AT25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU25">
         <v>0</v>
@@ -16942,8 +16942,8 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
-        <v>1</v>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <v>0</v>
       </c>
       <c r="G13">
         <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>

--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3260D85-398C-490C-9D06-F836C394DEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{511531B4-9181-44E9-9DE4-EC130AD9DF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="2" activeTab="5" xr2:uid="{926FECFB-B71C-4A2C-ACA6-D14493392182}"/>
+    <workbookView xWindow="2310" yWindow="1035" windowWidth="11385" windowHeight="15660" firstSheet="4" activeTab="5" xr2:uid="{926FECFB-B71C-4A2C-ACA6-D14493392182}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="RPS custom new" sheetId="7" r:id="rId2"/>
     <sheet name="CES custom" sheetId="8" r:id="rId3"/>
-    <sheet name="RPS v CES" sheetId="4" r:id="rId4"/>
-    <sheet name="default values" sheetId="5" r:id="rId5"/>
-    <sheet name="RQSD-BRQSD" sheetId="2" r:id="rId6"/>
-    <sheet name="RQSD-RQSD" sheetId="3" r:id="rId7"/>
+    <sheet name="IL Custom" sheetId="9" r:id="rId4"/>
+    <sheet name="VA custom" sheetId="10" r:id="rId5"/>
+    <sheet name="RPS v CES" sheetId="4" r:id="rId6"/>
+    <sheet name="default values" sheetId="5" r:id="rId7"/>
+    <sheet name="RQSD-BRQSD" sheetId="2" r:id="rId8"/>
+    <sheet name="RQSD-RQSD" sheetId="3" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="145">
   <si>
     <t>Source:</t>
   </si>
@@ -537,7 +539,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -553,6 +555,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,7 +588,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -600,6 +608,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="0" xfId="2" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -997,7 +1006,7 @@
   <dimension ref="A1:M50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="84.5703125" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1008,7 +1017,7 @@
         <v>73</v>
       </c>
       <c r="C1" s="12">
-        <v>45721</v>
+        <v>45723</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>39</v>
@@ -1605,10 +1614,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:K1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -8117,7 +8126,6 @@
         <v>0</v>
       </c>
       <c r="AG15">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AH15">
@@ -8911,7 +8919,7 @@
         <v>1</v>
       </c>
       <c r="AG20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH20">
         <v>1</v>
@@ -9066,7 +9074,7 @@
         <v>1</v>
       </c>
       <c r="AG21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH21">
         <v>1</v>
@@ -9221,7 +9229,7 @@
         <v>1</v>
       </c>
       <c r="AG22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH22">
         <v>1</v>
@@ -9376,7 +9384,7 @@
         <v>1</v>
       </c>
       <c r="AG23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH23">
         <v>1</v>
@@ -9531,7 +9539,7 @@
         <v>1</v>
       </c>
       <c r="AG24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH24">
         <v>1</v>
@@ -9920,6 +9928,4782 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD32CF9-981C-47B1-B896-3B13CED44A3B}">
+  <dimension ref="A1:AE25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1">
+        <v>2021</v>
+      </c>
+      <c r="C1">
+        <v>2022</v>
+      </c>
+      <c r="D1">
+        <v>2023</v>
+      </c>
+      <c r="E1">
+        <v>2024</v>
+      </c>
+      <c r="F1">
+        <v>2025</v>
+      </c>
+      <c r="G1">
+        <v>2026</v>
+      </c>
+      <c r="H1">
+        <v>2027</v>
+      </c>
+      <c r="I1">
+        <v>2028</v>
+      </c>
+      <c r="J1">
+        <v>2029</v>
+      </c>
+      <c r="K1">
+        <v>2030</v>
+      </c>
+      <c r="L1">
+        <v>2031</v>
+      </c>
+      <c r="M1">
+        <v>2032</v>
+      </c>
+      <c r="N1">
+        <v>2033</v>
+      </c>
+      <c r="O1">
+        <v>2034</v>
+      </c>
+      <c r="P1">
+        <v>2035</v>
+      </c>
+      <c r="Q1">
+        <v>2036</v>
+      </c>
+      <c r="R1">
+        <v>2037</v>
+      </c>
+      <c r="S1">
+        <v>2038</v>
+      </c>
+      <c r="T1">
+        <v>2039</v>
+      </c>
+      <c r="U1">
+        <v>2040</v>
+      </c>
+      <c r="V1">
+        <v>2041</v>
+      </c>
+      <c r="W1">
+        <v>2042</v>
+      </c>
+      <c r="X1">
+        <v>2043</v>
+      </c>
+      <c r="Y1">
+        <v>2044</v>
+      </c>
+      <c r="Z1">
+        <v>2045</v>
+      </c>
+      <c r="AA1">
+        <v>2046</v>
+      </c>
+      <c r="AB1">
+        <v>2047</v>
+      </c>
+      <c r="AC1">
+        <v>2048</v>
+      </c>
+      <c r="AD1">
+        <v>2049</v>
+      </c>
+      <c r="AE1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>1</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AE9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10">
+        <v>1</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AD10">
+        <v>1</v>
+      </c>
+      <c r="AE10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>1</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AE11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>1</v>
+      </c>
+      <c r="AB15">
+        <v>1</v>
+      </c>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AE15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>1</v>
+      </c>
+      <c r="Z18">
+        <v>1</v>
+      </c>
+      <c r="AA18">
+        <v>1</v>
+      </c>
+      <c r="AB18">
+        <v>1</v>
+      </c>
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AD18">
+        <v>1</v>
+      </c>
+      <c r="AE18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>1</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>1</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
+        <v>1</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
+        <v>1</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>1</v>
+      </c>
+      <c r="Z23">
+        <v>1</v>
+      </c>
+      <c r="AA23">
+        <v>1</v>
+      </c>
+      <c r="AB23">
+        <v>1</v>
+      </c>
+      <c r="AC23">
+        <v>1</v>
+      </c>
+      <c r="AD23">
+        <v>1</v>
+      </c>
+      <c r="AE23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1</v>
+      </c>
+      <c r="Z24">
+        <v>1</v>
+      </c>
+      <c r="AA24">
+        <v>1</v>
+      </c>
+      <c r="AB24">
+        <v>1</v>
+      </c>
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AD24">
+        <v>1</v>
+      </c>
+      <c r="AE24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE3D83DF-5C0A-4931-A0C7-8025ECBEB3FE}">
+  <dimension ref="A1:AE25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1">
+        <v>2021</v>
+      </c>
+      <c r="C1">
+        <v>2022</v>
+      </c>
+      <c r="D1">
+        <v>2023</v>
+      </c>
+      <c r="E1">
+        <v>2024</v>
+      </c>
+      <c r="F1">
+        <v>2025</v>
+      </c>
+      <c r="G1">
+        <v>2026</v>
+      </c>
+      <c r="H1">
+        <v>2027</v>
+      </c>
+      <c r="I1">
+        <v>2028</v>
+      </c>
+      <c r="J1">
+        <v>2029</v>
+      </c>
+      <c r="K1">
+        <v>2030</v>
+      </c>
+      <c r="L1">
+        <v>2031</v>
+      </c>
+      <c r="M1">
+        <v>2032</v>
+      </c>
+      <c r="N1">
+        <v>2033</v>
+      </c>
+      <c r="O1">
+        <v>2034</v>
+      </c>
+      <c r="P1">
+        <v>2035</v>
+      </c>
+      <c r="Q1">
+        <v>2036</v>
+      </c>
+      <c r="R1">
+        <v>2037</v>
+      </c>
+      <c r="S1">
+        <v>2038</v>
+      </c>
+      <c r="T1">
+        <v>2039</v>
+      </c>
+      <c r="U1">
+        <v>2040</v>
+      </c>
+      <c r="V1">
+        <v>2041</v>
+      </c>
+      <c r="W1">
+        <v>2042</v>
+      </c>
+      <c r="X1">
+        <v>2043</v>
+      </c>
+      <c r="Y1">
+        <v>2044</v>
+      </c>
+      <c r="Z1">
+        <v>2045</v>
+      </c>
+      <c r="AA1">
+        <v>2046</v>
+      </c>
+      <c r="AB1">
+        <v>2047</v>
+      </c>
+      <c r="AC1">
+        <v>2048</v>
+      </c>
+      <c r="AD1">
+        <v>2049</v>
+      </c>
+      <c r="AE1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>1</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AE9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10">
+        <v>1</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AD10">
+        <v>1</v>
+      </c>
+      <c r="AE10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>1</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AE11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>1</v>
+      </c>
+      <c r="AB15">
+        <v>1</v>
+      </c>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AE15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>1</v>
+      </c>
+      <c r="Z18">
+        <v>1</v>
+      </c>
+      <c r="AA18">
+        <v>1</v>
+      </c>
+      <c r="AB18">
+        <v>1</v>
+      </c>
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AD18">
+        <v>1</v>
+      </c>
+      <c r="AE18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>1</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>1</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
+        <v>1</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
+        <v>1</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>1</v>
+      </c>
+      <c r="Z23">
+        <v>1</v>
+      </c>
+      <c r="AA23">
+        <v>1</v>
+      </c>
+      <c r="AB23">
+        <v>1</v>
+      </c>
+      <c r="AC23">
+        <v>1</v>
+      </c>
+      <c r="AD23">
+        <v>1</v>
+      </c>
+      <c r="AE23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1</v>
+      </c>
+      <c r="Z24">
+        <v>1</v>
+      </c>
+      <c r="AA24">
+        <v>1</v>
+      </c>
+      <c r="AB24">
+        <v>1</v>
+      </c>
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AD24">
+        <v>1</v>
+      </c>
+      <c r="AE24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{095D0859-BFC7-40E6-97BE-4124316516E0}">
   <dimension ref="A1:AH53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11250,98 +16034,98 @@
       <c r="C16" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="L16" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="N16" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="O16" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="P16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="R16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="S16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="T16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="U16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="V16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="W16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="X16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="Z16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AA16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AD16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AE16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AF16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AH16" s="11" t="s">
-        <v>141</v>
+      <c r="D16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="N16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="O16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="P16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="R16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="S16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="T16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="U16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="V16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="W16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="X16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH16" s="15" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="2:34" x14ac:dyDescent="0.25">
@@ -14583,98 +19367,98 @@
       <c r="C49" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="D49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="F49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="G49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="H49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="I49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="K49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="L49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="M49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="N49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="O49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="P49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="R49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="S49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="T49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="U49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="V49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="W49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="X49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="Z49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AA49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AD49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AE49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AF49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG49" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="AH49" s="11" t="s">
-        <v>141</v>
+      <c r="D49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="H49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="I49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="J49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="K49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="L49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="M49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="N49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="O49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="P49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="R49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="S49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="T49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="U49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="V49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="W49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="X49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG49" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH49" s="15" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="50" spans="2:34" x14ac:dyDescent="0.25">
@@ -15094,7 +19878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14CC2A82-7998-436D-923D-E027ED704B93}">
   <dimension ref="A2:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15439,7 +20223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -15551,123 +20335,153 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="C2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="D2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="E2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="F2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="G2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="H2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="I2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="J2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="K2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="L2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="M2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="N2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="O2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="P2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="Q2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="R2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="S2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="T2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="U2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="V2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="W2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="X2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="Y2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="Z2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="AA2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="AB2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="AC2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="AD2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
       <c r="AE2">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,'default values'!$C3)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE2,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE2,
+'default values'!$C3)))</f>
         <v>0</v>
       </c>
     </row>
@@ -15676,123 +20490,153 @@
         <v>30</v>
       </c>
       <c r="B3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="C3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="D3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="E3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="F3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="G3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="H3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="I3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="J3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="K3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="L3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="M3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="N3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="P3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="R3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="U3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="V3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="W3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="X3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,'default values'!$C4)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE3,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE3,
+'default values'!$C4)))</f>
         <v>0</v>
       </c>
     </row>
@@ -15801,123 +20645,153 @@
         <v>31</v>
       </c>
       <c r="B4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="C4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="D4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="E4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="F4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="G4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="H4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="I4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="J4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="K4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="L4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="M4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="N4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="P4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="R4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="S4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="T4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="U4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="V4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="W4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="X4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,'default values'!$C5)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE4,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE4,
+'default values'!$C5)))</f>
         <v>0</v>
       </c>
     </row>
@@ -15926,123 +20800,153 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="C5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="D5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="E5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="F5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="G5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="H5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="I5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="J5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="K5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="L5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="M5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="N5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="O5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="P5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="Q5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="R5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="S5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="T5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="U5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="V5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="W5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="X5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="Y5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="Z5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="AA5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="AB5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="AC5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="AD5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
       <c r="AE5">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,'default values'!$C6)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE5,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE5,
+'default values'!$C6)))</f>
         <v>1</v>
       </c>
     </row>
@@ -16051,123 +20955,153 @@
         <v>3</v>
       </c>
       <c r="B6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="C6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="D6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="E6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="F6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="G6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="H6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="I6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="J6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="K6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="L6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="M6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="N6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="O6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="P6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="Q6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="R6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="S6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="T6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="U6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="V6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="W6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="X6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="Y6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="Z6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="AA6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="AB6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="AC6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="AD6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
       <c r="AE6">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,'default values'!$C7)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE6,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE6,
+'default values'!$C7)))</f>
         <v>1</v>
       </c>
     </row>
@@ -16176,123 +21110,153 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="C7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="D7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="E7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="F7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="G7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="H7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="I7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="J7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="K7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="L7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="M7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="N7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="O7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="P7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="Q7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="R7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="S7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="T7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="U7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="V7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="W7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="X7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="Y7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="Z7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="AA7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="AB7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="AC7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="AD7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
       <c r="AE7">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,'default values'!$C8)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE7,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE7,
+'default values'!$C8)))</f>
         <v>1</v>
       </c>
     </row>
@@ -16301,123 +21265,153 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="C8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="D8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="E8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="F8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="G8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="H8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="I8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="J8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="K8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="L8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="M8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="N8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="O8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="P8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="Q8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="R8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="S8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="T8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="U8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="V8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="W8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="X8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="Y8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="Z8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="AA8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="AB8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="AC8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="AD8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
       <c r="AE8">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,'default values'!$C9)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE8,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE8,
+'default values'!$C9)))</f>
         <v>1</v>
       </c>
     </row>
@@ -16426,123 +21420,153 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="C9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="D9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="E9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="F9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="G9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="H9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="I9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="J9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="K9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="L9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="M9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="N9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="O9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="P9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="Q9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="R9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="S9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="T9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="U9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="V9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="W9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="X9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="Y9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="Z9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="AA9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="AB9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="AC9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="AD9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
       <c r="AE9">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,'default values'!$C10)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE9,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE9,
+'default values'!$C10)))</f>
         <v>1</v>
       </c>
     </row>
@@ -16551,123 +21575,153 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="C10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="D10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="E10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="F10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="G10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="H10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="I10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="J10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="K10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="L10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="M10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="N10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="O10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="P10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="Q10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="R10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="S10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="T10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="U10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="V10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="W10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="X10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="Y10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="Z10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="AA10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="AB10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="AC10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="AD10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
       <c r="AE10">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,'default values'!$C11)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE10,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE10,
+'default values'!$C11)))</f>
         <v>1</v>
       </c>
     </row>
@@ -16676,123 +21730,153 @@
         <v>7</v>
       </c>
       <c r="B11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="C11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="D11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="E11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="F11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="G11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="H11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="I11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="J11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="K11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="L11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="M11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="N11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="O11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="P11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="Q11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="R11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="S11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="T11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="U11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="V11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="W11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="X11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="Y11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="Z11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="AA11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="AB11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="AC11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="AD11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
       <c r="AE11">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,'default values'!$C12)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE11,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE11,
+'default values'!$C12)))</f>
         <v>1</v>
       </c>
     </row>
@@ -16801,123 +21885,153 @@
         <v>8</v>
       </c>
       <c r="B12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="C12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="D12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="E12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="F12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="G12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="H12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="I12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="J12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="K12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="L12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="M12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="N12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="P12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="R12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="S12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="T12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="U12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="V12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="W12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="X12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="Y12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="AA12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="AB12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="AC12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="AD12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
       <c r="AE12">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,'default values'!$C13)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE12,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE12,
+'default values'!$C13)))</f>
         <v>0</v>
       </c>
     </row>
@@ -16926,123 +22040,153 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="C13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="D13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="E13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="F13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="G13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="H13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="I13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="J13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="K13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="L13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="M13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="N13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="O13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="P13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="Q13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="R13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="S13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="T13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="U13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="V13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="W13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="X13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="Y13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="AA13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="AB13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="AC13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,'default values'!$C14)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE13,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE13,
+'default values'!$C14)))</f>
         <v>0</v>
       </c>
     </row>
@@ -17051,123 +22195,153 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="C14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="D14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="E14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="F14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="G14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="H14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="I14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="J14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="K14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="L14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="M14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="N14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="O14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="P14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="Q14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="R14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="S14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="T14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="U14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="V14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="W14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="X14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,'default values'!$C15)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE14,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE14,
+'default values'!$C15)))</f>
         <v>0</v>
       </c>
     </row>
@@ -17176,123 +22350,153 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="C15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="D15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="E15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="F15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="G15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="H15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="I15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="J15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="K15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="L15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="M15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="N15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="O15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="P15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="Q15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="R15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="S15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="T15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="U15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="V15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="W15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="X15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="Y15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="Z15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="AA15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="AB15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="AC15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="AD15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
       <c r="AE15">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,'default values'!$C16)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE15,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE15,
+'default values'!$C16)))</f>
         <v>1</v>
       </c>
     </row>
@@ -17301,123 +22505,153 @@
         <v>26</v>
       </c>
       <c r="B16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="C16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="D16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="E16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="F16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="G16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="H16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="I16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="J16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="K16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="L16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="M16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="N16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="O16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="P16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="Q16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="R16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="S16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="T16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="U16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="V16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="W16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="X16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="Y16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="Z16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="AA16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="AB16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="AC16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="AD16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
       <c r="AE16">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,'default values'!$C17)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE16,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE16,
+'default values'!$C17)))</f>
         <v>0</v>
       </c>
     </row>
@@ -17426,123 +22660,153 @@
         <v>27</v>
       </c>
       <c r="B17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="C17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="D17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="E17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="F17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="G17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="H17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="I17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="J17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="K17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="L17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="M17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="N17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="O17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="P17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="Q17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="R17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="S17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="T17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="U17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="V17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="W17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="X17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="Y17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="Z17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="AA17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="AB17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="AC17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="AD17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
       <c r="AE17">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,'default values'!$C18)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE17,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE17,
+'default values'!$C18)))</f>
         <v>0</v>
       </c>
     </row>
@@ -17551,123 +22815,153 @@
         <v>28</v>
       </c>
       <c r="B18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="C18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="D18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="E18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="F18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="G18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="H18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="I18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="J18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="K18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="L18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="M18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="N18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="O18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="P18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="Q18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="R18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="S18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="T18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="U18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="V18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="W18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="X18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="Y18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="Z18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="AA18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="AB18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="AC18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="AD18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
       <c r="AE18">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,'default values'!$C19)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE18,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE18,
+'default values'!$C19)))</f>
         <v>1</v>
       </c>
     </row>
@@ -17676,123 +22970,153 @@
         <v>32</v>
       </c>
       <c r="B19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="C19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="D19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="E19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="F19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="G19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="H19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="I19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="J19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="K19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="L19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="M19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="N19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="O19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="P19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="Q19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="R19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="S19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="T19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="U19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="V19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="W19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="X19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="Y19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="Z19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="AA19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="AB19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="AC19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="AD19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
       <c r="AE19">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,'default values'!$C20)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE19,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE19,
+'default values'!$C20)))</f>
         <v>1</v>
       </c>
     </row>
@@ -17801,123 +23125,153 @@
         <v>33</v>
       </c>
       <c r="B20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="C20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="D20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="E20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="F20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="G20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="H20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="I20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="J20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="K20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="L20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="M20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="N20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="O20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="P20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="Q20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="R20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="S20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="T20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="U20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="V20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="W20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="X20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="Y20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="Z20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="AA20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="AB20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="AC20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="AD20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
       <c r="AE20">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,'default values'!$C21)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE20,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE20,
+'default values'!$C21)))</f>
         <v>1</v>
       </c>
     </row>
@@ -17926,123 +23280,153 @@
         <v>34</v>
       </c>
       <c r="B21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="C21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="D21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="E21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="F21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="G21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="H21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="I21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="J21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="K21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="L21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="M21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="N21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="O21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="P21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="Q21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="R21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="S21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="T21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="U21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="V21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="W21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="X21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="Y21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="Z21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="AA21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="AB21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="AC21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="AD21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
       <c r="AE21">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,'default values'!$C22)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE21,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE21,
+'default values'!$C22)))</f>
         <v>1</v>
       </c>
     </row>
@@ -18051,123 +23435,153 @@
         <v>35</v>
       </c>
       <c r="B22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="C22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="D22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="E22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="F22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="G22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="H22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="I22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="J22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="K22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="L22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="M22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="N22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="O22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="P22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="Q22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="R22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="S22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="T22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="U22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="V22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="W22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="X22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="Y22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="Z22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="AA22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="AB22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="AC22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="AD22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
       <c r="AE22">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,'default values'!$C23)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE22,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE22,
+'default values'!$C23)))</f>
         <v>1</v>
       </c>
     </row>
@@ -18176,123 +23590,153 @@
         <v>36</v>
       </c>
       <c r="B23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="C23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="D23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="E23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="F23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="G23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="H23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="I23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="J23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="K23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="L23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="M23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="N23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="O23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="P23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="Q23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="R23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="S23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="T23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="U23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="V23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="W23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="X23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="Y23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="Z23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="AA23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="AB23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="AC23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="AD23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
       <c r="AE23">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,'default values'!$C24)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE23,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE23,
+'default values'!$C24)))</f>
         <v>1</v>
       </c>
     </row>
@@ -18301,123 +23745,153 @@
         <v>37</v>
       </c>
       <c r="B24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="C24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="D24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="E24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="F24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="G24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="H24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="I24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="J24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="K24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="L24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="M24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="N24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="O24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="P24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="Q24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="R24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="S24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="T24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="U24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="V24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="W24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="X24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="Y24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="Z24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="AA24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="AB24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="AC24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="AD24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
       <c r="AE24">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,'default values'!$C25)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE24,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE24,
+'default values'!$C25)))</f>
         <v>1</v>
       </c>
     </row>
@@ -18426,123 +23900,153 @@
         <v>38</v>
       </c>
       <c r="B25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!B25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(B$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!B25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="C25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!C25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(C$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!C25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="D25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!D25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(D$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!D25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="E25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!E25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(E$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!E25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="F25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!F25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(F$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!F25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="G25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!G25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(G$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!G25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="H25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!H25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(H$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!H25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="I25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!I25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(I$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!I25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="J25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!J25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(J$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!J25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="K25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!K25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(K$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!K25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="L25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!L25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(L$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!L25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="M25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!M25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(M$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!M25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="N25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!N25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(N$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!N25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="O25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!O25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(O$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!O25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="P25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!P25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(P$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!P25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="Q25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Q25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Q$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Q25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="R25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!R25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(R$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!R25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="S25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!S25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(S$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!S25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="T25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!T25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(T$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!T25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="U25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!U25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(U$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!U25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="V25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!V25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(V$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!V25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="W25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!W25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(W$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!W25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="X25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!X25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(X$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!X25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="Y25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Y25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Y$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Y25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="Z25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!Z25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(Z$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!Z25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="AA25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AA25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AA$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AA25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="AB25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AB25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AB$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AB25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="AC25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AC25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AC$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AC25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="AD25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AD25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AD$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AD25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
       <c r="AE25">
-        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,'default values'!$C26)</f>
+        <f>IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="RPS",'default values'!$B26,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="IL",'IL Custom'!AE25,IF(INDEX('RPS v CES'!$D$4:$AH$53,MATCH(About!$B$2,'RPS v CES'!$C$4:$C$53,0),MATCH(AE$1,'RPS v CES'!$D$3:$AH$3,0))="VA",'VA custom'!AE25,
+'default values'!$C26)))</f>
         <v>0</v>
       </c>
     </row>
@@ -18556,7 +24060,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
